--- a/data/trans_dic/P16A07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 5,42</t>
+          <t>2,82; 5,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,81</t>
+          <t>3,76; 6,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,85</t>
+          <t>2,79; 5,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,86; 8,89</t>
+          <t>4,99; 9,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,64</t>
+          <t>8,31; 11,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 16,25</t>
+          <t>12,33; 16,27</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 13,64</t>
+          <t>9,37; 13,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,21; 14,75</t>
+          <t>11,37; 15,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 8,48</t>
+          <t>6,2; 8,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,25; 11,85</t>
+          <t>9,24; 11,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,94; 9,6</t>
+          <t>6,97; 9,61</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,17; 11,85</t>
+          <t>9,22; 11,94</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,63</t>
+          <t>0,64; 1,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,26</t>
+          <t>1,77; 3,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,39; 2,58</t>
+          <t>1,37; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,6</t>
+          <t>1,88; 3,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,54; 5,69</t>
+          <t>3,53; 5,55</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,83</t>
+          <t>4,5; 6,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,32</t>
+          <t>4,99; 7,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,48; 7,36</t>
+          <t>4,49; 7,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,42</t>
+          <t>2,2; 3,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 4,56</t>
+          <t>3,3; 4,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,35; 4,63</t>
+          <t>3,38; 4,67</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,23</t>
+          <t>3,53; 5,18</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,48</t>
+          <t>1,07; 3,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,0</t>
+          <t>0,67; 3,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,59</t>
+          <t>0,16; 1,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,82</t>
+          <t>1,23; 3,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,54</t>
+          <t>2,25; 5,6</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,83</t>
+          <t>1,0; 3,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 4,62</t>
+          <t>1,46; 4,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,31</t>
+          <t>2,76; 5,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 3,93</t>
+          <t>1,93; 4,11</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,32</t>
+          <t>1,18; 3,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,61</t>
+          <t>0,92; 2,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,97</t>
+          <t>2,19; 3,95</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,62</t>
+          <t>1,68; 2,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 3,74</t>
+          <t>2,52; 3,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,75</t>
+          <t>1,71; 2,8</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,95</t>
+          <t>2,45; 3,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,3</t>
+          <t>5,65; 7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,37; 9,23</t>
+          <t>7,46; 9,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,05</t>
+          <t>6,19; 7,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,02</t>
+          <t>5,81; 8,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 4,81</t>
+          <t>3,89; 4,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 6,35</t>
+          <t>5,23; 6,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,16; 5,21</t>
+          <t>4,17; 5,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 5,8</t>
+          <t>4,56; 5,81</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha consumido antidepresivos en las dos últimas semanas</t>
+          <t>Población que ha consumido antidepresivos en las dos últimas semanas (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>30083; 55952</t>
+          <t>29067; 55338</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>35685; 66230</t>
+          <t>36546; 66248</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21620; 44154</t>
+          <t>21043; 44190</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>24961; 45634</t>
+          <t>25614; 46955</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109252; 153103</t>
+          <t>109256; 152335</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>165006; 216579</t>
+          <t>164313; 216833</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93670; 135694</t>
+          <t>93234; 134735</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84281; 110900</t>
+          <t>85499; 112940</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>146762; 199114</t>
+          <t>145453; 196606</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>213100; 273013</t>
+          <t>212995; 270172</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121311; 167894</t>
+          <t>121978; 168122</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>116077; 149973</t>
+          <t>116605; 151063</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10421; 27527</t>
+          <t>10852; 27334</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33662; 63840</t>
+          <t>34681; 63481</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28878; 53630</t>
+          <t>28384; 53751</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43380; 82476</t>
+          <t>43075; 83020</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56197; 90363</t>
+          <t>55993; 88193</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78494; 119733</t>
+          <t>78858; 119679</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>102619; 145512</t>
+          <t>99200; 145772</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100199; 164560</t>
+          <t>100360; 166108</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73440; 112165</t>
+          <t>72168; 109540</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>118599; 169282</t>
+          <t>122651; 173147</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>136367; 188046</t>
+          <t>137227; 189645</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>164390; 236903</t>
+          <t>160003; 234707</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5789; 19212</t>
+          <t>5913; 20080</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3860; 19207</t>
+          <t>3216; 19058</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>885; 8681</t>
+          <t>885; 7981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8115; 24686</t>
+          <t>7923; 24174</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9797; 26403</t>
+          <t>10714; 26657</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4756; 17527</t>
+          <t>4575; 18247</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8501; 25355</t>
+          <t>8000; 25362</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18006; 35047</t>
+          <t>18220; 35232</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19682; 40407</t>
+          <t>19805; 42239</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10049; 31151</t>
+          <t>11073; 30063</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9841; 28586</t>
+          <t>10132; 28578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29784; 51882</t>
+          <t>28641; 51680</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55089; 85755</t>
+          <t>55132; 88484</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>84587; 127464</t>
+          <t>86017; 133067</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>58053; 92805</t>
+          <t>57906; 94451</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85743; 136191</t>
+          <t>84603; 135418</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190280; 246748</t>
+          <t>190996; 247695</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>261124; 327167</t>
+          <t>264389; 335130</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>218891; 284486</t>
+          <t>218483; 279133</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>217257; 292827</t>
+          <t>212173; 292825</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>255230; 320257</t>
+          <t>259067; 319516</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>363046; 441640</t>
+          <t>363556; 446581</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>287392; 360065</t>
+          <t>287840; 360314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>324786; 411496</t>
+          <t>323657; 412193</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P16A07-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P16A07-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,36</t>
+          <t>2,93; 5,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 6,82</t>
+          <t>3,84; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,86</t>
+          <t>2,97; 6,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,14</t>
+          <t>4,49; 8,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,31; 11,58</t>
+          <t>8,29; 11,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 16,27</t>
+          <t>12,55; 16,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 13,55</t>
+          <t>9,35; 13,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11,37; 15,02</t>
+          <t>11,42; 15,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,2; 8,38</t>
+          <t>6,19; 8,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9,24; 11,72</t>
+          <t>9,24; 11,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,97; 9,61</t>
+          <t>6,94; 9,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,22; 11,94</t>
+          <t>8,91; 11,68</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,62</t>
+          <t>0,64; 1,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,77; 3,24</t>
+          <t>1,77; 3,23</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,59</t>
+          <t>1,35; 2,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 3,62</t>
+          <t>2,53; 4,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,55</t>
+          <t>3,53; 5,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,83</t>
+          <t>4,49; 6,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,99; 7,33</t>
+          <t>5,14; 7,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,49; 7,43</t>
+          <t>6,05; 7,92</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,34</t>
+          <t>2,21; 3,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,3; 4,66</t>
+          <t>3,26; 4,6</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 4,67</t>
+          <t>3,37; 4,7</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,53; 5,18</t>
+          <t>4,43; 5,64</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 3,64</t>
+          <t>1,03; 3,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,97</t>
+          <t>0,66; 4,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,46</t>
+          <t>0,16; 1,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 3,74</t>
+          <t>1,17; 3,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,25; 5,6</t>
+          <t>2,08; 5,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,99</t>
+          <t>1,05; 3,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,62</t>
+          <t>1,52; 4,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,76; 5,33</t>
+          <t>2,64; 5,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,11</t>
+          <t>1,88; 3,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,18; 3,21</t>
+          <t>1,17; 3,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,61</t>
+          <t>0,97; 2,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,95</t>
+          <t>2,2; 3,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,7</t>
+          <t>1,68; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,9</t>
+          <t>2,54; 3,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,8</t>
+          <t>1,73; 2,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,92</t>
+          <t>2,88; 4,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 7,33</t>
+          <t>5,64; 7,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,46; 9,46</t>
+          <t>7,47; 9,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,19; 7,9</t>
+          <t>6,1; 7,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,81; 8,02</t>
+          <t>6,96; 8,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,89; 4,8</t>
+          <t>3,86; 4,86</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,42</t>
+          <t>5,28; 6,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 5,21</t>
+          <t>4,18; 5,23</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,56; 5,81</t>
+          <t>5,15; 6,11</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34333</t>
+          <t>36065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>98103</t>
+          <t>108325</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>132436</t>
+          <t>144391</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>29067; 55338</t>
+          <t>30249; 55241</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>36546; 66248</t>
+          <t>37280; 67037</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21043; 44190</t>
+          <t>22419; 45517</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25614; 46955</t>
+          <t>25936; 48313</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>109256; 152335</t>
+          <t>109014; 155845</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>164313; 216833</t>
+          <t>167225; 220482</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93234; 134735</t>
+          <t>93022; 133587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85499; 112940</t>
+          <t>93653; 123840</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>145453; 196606</t>
+          <t>145255; 198921</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>212995; 270172</t>
+          <t>212969; 274997</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>121978; 168122</t>
+          <t>121320; 167452</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>116605; 151063</t>
+          <t>124448; 163185</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63192</t>
+          <t>71085</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>138356</t>
+          <t>149330</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>201548</t>
+          <t>220415</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10852; 27334</t>
+          <t>10758; 26893</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>34681; 63481</t>
+          <t>34629; 63303</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28384; 53751</t>
+          <t>28070; 53689</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>43075; 83020</t>
+          <t>56325; 89777</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>55993; 88193</t>
+          <t>56090; 89923</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>78858; 119679</t>
+          <t>78608; 118767</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>99200; 145772</t>
+          <t>102191; 146328</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>100360; 166108</t>
+          <t>131299; 172022</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>72168; 109540</t>
+          <t>72638; 108568</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>122651; 173147</t>
+          <t>121125; 170677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>137227; 189645</t>
+          <t>137166; 190839</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>160003; 234707</t>
+          <t>195094; 248060</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14232</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>27933</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39379</t>
+          <t>42537</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5913; 20080</t>
+          <t>5696; 17943</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3216; 19058</t>
+          <t>3189; 19414</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>885; 7981</t>
+          <t>882; 8133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7923; 24174</t>
+          <t>8297; 24398</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10714; 26657</t>
+          <t>9905; 26796</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4575; 18247</t>
+          <t>4783; 17710</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8000; 25362</t>
+          <t>8322; 24343</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18220; 35232</t>
+          <t>19437; 38321</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19805; 42239</t>
+          <t>19289; 40176</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11073; 30063</t>
+          <t>10929; 31696</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10132; 28578</t>
+          <t>10620; 29388</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28641; 51680</t>
+          <t>31816; 55733</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>111757</t>
+          <t>121754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>261606</t>
+          <t>285588</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>373363</t>
+          <t>407343</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>55132; 88484</t>
+          <t>54910; 87621</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>86017; 133067</t>
+          <t>86761; 132115</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57906; 94451</t>
+          <t>58559; 93367</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>84603; 135418</t>
+          <t>101296; 145347</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190996; 247695</t>
+          <t>190667; 247809</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>264389; 335130</t>
+          <t>264632; 332118</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>218483; 279133</t>
+          <t>215445; 280598</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>212173; 292825</t>
+          <t>259389; 313804</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>259067; 319516</t>
+          <t>256746; 323336</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>363556; 446581</t>
+          <t>366947; 449457</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>287840; 360314</t>
+          <t>288860; 361407</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>323657; 412193</t>
+          <t>372853; 442950</t>
         </is>
       </c>
     </row>
